--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -272,7 +272,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik</t>
+    <t>anamneseUndDiagnostik</t>
   </si>
   <si>
     <t>Event</t>
@@ -566,7 +566,7 @@
     <t>Identifies categories of clinical impressions.  This is a place-holder only.  It may be removed.</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Untersuchungsanlass</t>
+    <t>anamneseUndDiagnostik.untersuchungsanlass</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -629,7 +629,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Untersuchungsdatum</t>
+    <t>anamneseUndDiagnostik.untersuchungsdatum</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -848,7 +848,7 @@
     <t>e.g. The patient is a pregnant, has congestive heart failure, has an Adenocarcinoma, and is allergic to penicillin.</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.KlinischeDiagnose</t>
+    <t>anamneseUndDiagnostik.klinischeDiagnose</t>
   </si>
   <si>
     <t>PRB-3 / IAM-7</t>
@@ -908,7 +908,7 @@
     <t>http://hl7.org/fhir/ValueSet/investigation-sets|4.0.1</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.MethodeDiagnosestellung</t>
+    <t>anamneseUndDiagnostik.methodeDiagnosestellung</t>
   </si>
   <si>
     <t>ClinicalImpression.investigation.item</t>
@@ -927,7 +927,7 @@
     <t>Most investigations are observations of one kind or another but some other specific types of data collection resources can also be used.</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Phaenotypisierung</t>
+    <t>anamneseUndDiagnostik.phaenotypisierung</t>
   </si>
   <si>
     <t>OBX-21</t>
@@ -984,7 +984,7 @@
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/ValueSet/mii-vs-seltene-hpo-phenotypic-observation-codes</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Phaenotypisierung.HPOTerm</t>
+    <t>anamneseUndDiagnostik.phaenotypisierung.hpoTerm</t>
   </si>
   <si>
     <t>ClinicalImpression.finding.itemReference</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -604,7 +604,7 @@
     <t>Group is typically for veterinary and/or public health purposes.</t>
   </si>
   <si>
-    <t>Patient</t>
+    <t>persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-impression.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
